--- a/data/trans_orig/P04B3_2_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P04B3_2_2023-Edad-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si percibe la temperatura en la vivienda durante el invierno como un problema en 2023</t>
+          <t>Población según si percibe la temperatura en la vivienda durante el invierno como un problema en 2023 (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>51309</t>
+          <t>51801</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>99804</t>
+          <t>97094</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>24,95%</t>
+          <t>24,27%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>45913</t>
+          <t>44500</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>78564</t>
+          <t>77455</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14,66%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>25,08%</t>
+          <t>24,73%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>104414</t>
+          <t>104153</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>157818</t>
+          <t>160601</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,13%</t>
+          <t>22,52%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>22185</t>
+          <t>23472</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>60370</t>
+          <t>61806</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>15,09%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>28930</t>
+          <t>29394</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>60581</t>
+          <t>60699</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>19,34%</t>
+          <t>19,38%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>61731</t>
+          <t>62583</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>113556</t>
+          <t>112314</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>15,75%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>51583</t>
+          <t>50854</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>110499</t>
+          <t>111983</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12,9%</t>
+          <t>12,71%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>27,63%</t>
+          <t>28,0%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>34025</t>
+          <t>33834</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>69552</t>
+          <t>69857</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>22,21%</t>
+          <t>22,3%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>98542</t>
+          <t>94019</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>166152</t>
+          <t>163455</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>23,3%</t>
+          <t>22,92%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>175073</t>
+          <t>175909</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>241746</t>
+          <t>243956</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>43,77%</t>
+          <t>43,98%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>60,44%</t>
+          <t>60,99%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>136415</t>
+          <t>140016</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>186190</t>
+          <t>184433</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>43,56%</t>
+          <t>44,71%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>59,45%</t>
+          <t>58,89%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>330633</t>
+          <t>323744</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>410549</t>
+          <t>410002</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>46,36%</t>
+          <t>45,39%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>57,57%</t>
+          <t>57,49%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>71632</t>
+          <t>72391</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>111081</t>
+          <t>113370</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>16,92%</t>
+          <t>17,1%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>26,24%</t>
+          <t>26,78%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>87722</t>
+          <t>89971</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>299873</t>
+          <t>300198</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>58,58%</t>
+          <t>58,64%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>176331</t>
+          <t>177075</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>422545</t>
+          <t>386525</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>18,93%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>45,18%</t>
+          <t>41,33%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>38215</t>
+          <t>36308</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>72082</t>
+          <t>70594</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>16,67%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>31597</t>
+          <t>30147</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>68535</t>
+          <t>68130</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>77457</t>
+          <t>77254</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>129197</t>
+          <t>127452</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>8,26%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>13,63%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>59978</t>
+          <t>60608</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>104395</t>
+          <t>108698</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>24,66%</t>
+          <t>25,67%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>50921</t>
+          <t>52672</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>107210</t>
+          <t>108305</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>20,94%</t>
+          <t>21,16%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>125953</t>
+          <t>129416</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>200290</t>
+          <t>199827</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>21,41%</t>
+          <t>21,36%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>173825</t>
+          <t>173400</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>225752</t>
+          <t>225714</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>41,06%</t>
+          <t>40,96%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>53,32%</t>
+          <t>53,31%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>134530</t>
+          <t>132259</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>268857</t>
+          <t>266348</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>26,28%</t>
+          <t>25,84%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>52,52%</t>
+          <t>52,03%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>320401</t>
+          <t>333498</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>472858</t>
+          <t>471031</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>34,26%</t>
+          <t>35,66%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>50,56%</t>
+          <t>50,36%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>82819</t>
+          <t>83543</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>119376</t>
+          <t>118728</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>15,58%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>22,26%</t>
+          <t>22,14%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>76092</t>
+          <t>74691</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>119139</t>
+          <t>119279</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12,87%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>20,16%</t>
+          <t>20,18%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>170690</t>
+          <t>171756</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>227334</t>
+          <t>227475</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>15,14%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>20,17%</t>
+          <t>20,18%</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>48477</t>
+          <t>49411</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>79834</t>
+          <t>79400</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1996,12 +1996,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>14,89%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2016,12 +2016,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>44309</t>
+          <t>44050</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>75199</t>
+          <t>75291</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>12,74%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2051,12 +2051,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>101448</t>
+          <t>102616</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>142937</t>
+          <t>144252</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>9,0%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>12,8%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>84956</t>
+          <t>83271</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>122703</t>
+          <t>121865</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,84%</t>
+          <t>15,53%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>22,88%</t>
+          <t>22,73%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>71521</t>
+          <t>73016</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>115643</t>
+          <t>115449</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>12,35%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>168418</t>
+          <t>168365</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>226953</t>
+          <t>229404</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>20,35%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>241920</t>
+          <t>245678</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>291186</t>
+          <t>294334</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>45,12%</t>
+          <t>45,82%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>54,31%</t>
+          <t>54,9%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>302115</t>
+          <t>299410</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>396398</t>
+          <t>398664</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>51,11%</t>
+          <t>50,65%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>67,06%</t>
+          <t>67,44%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>561346</t>
+          <t>560786</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>679607</t>
+          <t>676348</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>49,8%</t>
+          <t>49,75%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>60,29%</t>
+          <t>60,0%</t>
         </is>
       </c>
     </row>
@@ -2437,12 +2437,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>44678</t>
+          <t>44932</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>149866</t>
+          <t>149446</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>16,83%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>109061</t>
+          <t>106532</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>152083</t>
+          <t>150019</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>21,38%</t>
+          <t>21,09%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>136631</t>
+          <t>133487</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>282790</t>
+          <t>285670</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,54%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>17,68%</t>
+          <t>17,86%</t>
         </is>
       </c>
     </row>
@@ -2550,12 +2550,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>35836</t>
+          <t>41016</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>139408</t>
+          <t>137930</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>81261</t>
+          <t>81477</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>115431</t>
+          <t>112744</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2600,12 +2600,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>16,23%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>116266</t>
+          <t>111199</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>236562</t>
+          <t>239567</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>6,95%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>14,98%</t>
         </is>
       </c>
     </row>
@@ -2663,12 +2663,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>49843</t>
+          <t>48795</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>168892</t>
+          <t>170928</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>19,25%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2698,12 +2698,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>104153</t>
+          <t>103958</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>140132</t>
+          <t>141044</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>19,7%</t>
+          <t>19,83%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>144137</t>
+          <t>146576</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>295951</t>
+          <t>296126</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>18,51%</t>
+          <t>18,52%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>445223</t>
+          <t>444264</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>750298</t>
+          <t>757394</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>50,15%</t>
+          <t>50,04%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>84,51%</t>
+          <t>85,31%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>331625</t>
+          <t>333825</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>412560</t>
+          <t>412001</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>46,61%</t>
+          <t>46,92%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>57,99%</t>
+          <t>57,91%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>799858</t>
+          <t>795965</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1210104</t>
+          <t>1204651</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>50,02%</t>
+          <t>49,77%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>75,67%</t>
+          <t>75,33%</t>
         </is>
       </c>
     </row>
@@ -3006,12 +3006,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>88849</t>
+          <t>89659</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>122205</t>
+          <t>123315</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3021,12 +3021,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>21,97%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3041,12 +3041,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>95589</t>
+          <t>96656</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>123883</t>
+          <t>124563</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>17,66%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>22,64%</t>
+          <t>22,76%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3076,12 +3076,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>194271</t>
+          <t>195630</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>239482</t>
+          <t>239243</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>17,65%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>21,6%</t>
+          <t>21,58%</t>
         </is>
       </c>
     </row>
@@ -3119,12 +3119,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>74148</t>
+          <t>74083</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>107113</t>
+          <t>107096</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3134,47 +3134,47 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
+          <t>13,2%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>19,08%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>149</t>
+        </is>
+      </c>
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>84619</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
+        <is>
+          <t>72317</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>98669</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>15,46%</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
           <t>13,21%</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>19,09%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>149</t>
-        </is>
-      </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>84619</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
-        <is>
-          <t>71725</t>
-        </is>
-      </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>97836</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>15,46%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>13,11%</t>
-        </is>
-      </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3189,12 +3189,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>153061</t>
+          <t>154136</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>195191</t>
+          <t>196626</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>13,9%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>17,74%</t>
         </is>
       </c>
     </row>
@@ -3232,12 +3232,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>97411</t>
+          <t>96419</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>132615</t>
+          <t>132942</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3247,12 +3247,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>17,18%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>23,63%</t>
+          <t>23,69%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3267,12 +3267,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>82793</t>
+          <t>83867</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>109439</t>
+          <t>110631</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>15,32%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>20,21%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3302,12 +3302,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>188724</t>
+          <t>188890</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>232527</t>
+          <t>233422</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>17,04%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>21,06%</t>
         </is>
       </c>
     </row>
@@ -3345,12 +3345,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>231684</t>
+          <t>230547</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>274211</t>
+          <t>276171</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3360,12 +3360,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>41,28%</t>
+          <t>41,08%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>48,86%</t>
+          <t>49,21%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>239144</t>
+          <t>237924</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>272016</t>
+          <t>271476</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3395,12 +3395,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>43,7%</t>
+          <t>43,47%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>49,7%</t>
+          <t>49,6%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>481919</t>
+          <t>480068</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>537541</t>
+          <t>537902</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3430,12 +3430,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>43,47%</t>
+          <t>43,31%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>48,49%</t>
+          <t>48,52%</t>
         </is>
       </c>
     </row>
@@ -3575,12 +3575,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>59271</t>
+          <t>60407</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>82176</t>
+          <t>82748</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3590,12 +3590,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>16,41%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>22,32%</t>
+          <t>22,48%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>28649</t>
+          <t>29978</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>106665</t>
+          <t>108226</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>17,53%</t>
+          <t>17,79%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3645,12 +3645,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>76538</t>
+          <t>74825</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>182885</t>
+          <t>183038</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>18,74%</t>
         </is>
       </c>
     </row>
@@ -3688,12 +3688,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>44236</t>
+          <t>43523</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>66027</t>
+          <t>66438</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3703,12 +3703,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>18,05%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>24325</t>
+          <t>24891</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>94488</t>
+          <t>95216</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3738,12 +3738,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3758,12 +3758,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>61816</t>
+          <t>61289</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>149287</t>
+          <t>150280</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3773,12 +3773,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>15,29%</t>
+          <t>15,39%</t>
         </is>
       </c>
     </row>
@@ -3801,12 +3801,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>61084</t>
+          <t>61607</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>86287</t>
+          <t>87291</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>16,73%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>23,44%</t>
+          <t>23,71%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3836,12 +3836,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>31470</t>
+          <t>33478</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>115942</t>
+          <t>116996</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3851,12 +3851,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>19,06%</t>
+          <t>19,23%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3871,12 +3871,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>78274</t>
+          <t>78197</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>192508</t>
+          <t>193348</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3886,12 +3886,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>8,01%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>19,8%</t>
         </is>
       </c>
     </row>
@@ -3914,12 +3914,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>155260</t>
+          <t>154947</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>185732</t>
+          <t>184994</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3929,12 +3929,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>42,17%</t>
+          <t>42,09%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>50,45%</t>
+          <t>50,25%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3949,12 +3949,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>299178</t>
+          <t>297350</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>522520</t>
+          <t>515999</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3964,12 +3964,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>49,18%</t>
+          <t>48,88%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>85,89%</t>
+          <t>84,82%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3984,12 +3984,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>462180</t>
+          <t>462827</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>758572</t>
+          <t>760170</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3999,12 +3999,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>47,33%</t>
+          <t>47,39%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>77,68%</t>
+          <t>77,84%</t>
         </is>
       </c>
     </row>
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>40922</t>
+          <t>40779</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>60348</t>
+          <t>60467</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4159,12 +4159,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>14,42%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>21,38%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>65497</t>
+          <t>65626</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>88958</t>
+          <t>89212</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>15,38%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>20,95%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>111085</t>
+          <t>113230</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>140623</t>
+          <t>142238</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>15,98%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>20,07%</t>
         </is>
       </c>
     </row>
@@ -4257,12 +4257,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>38719</t>
+          <t>37602</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>58101</t>
+          <t>58362</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4272,12 +4272,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>20,64%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4292,12 +4292,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>58035</t>
+          <t>58666</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>79088</t>
+          <t>78602</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4307,12 +4307,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>18,57%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4327,12 +4327,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>101422</t>
+          <t>101178</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>128811</t>
+          <t>130536</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>14,31%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>18,18%</t>
+          <t>18,42%</t>
         </is>
       </c>
     </row>
@@ -4370,12 +4370,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>50531</t>
+          <t>50552</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>73312</t>
+          <t>74054</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4385,12 +4385,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>17,88%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>25,93%</t>
+          <t>26,19%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4405,12 +4405,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>74376</t>
+          <t>75320</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>98406</t>
+          <t>98475</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4420,12 +4420,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>17,47%</t>
+          <t>17,69%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>23,11%</t>
+          <t>23,13%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4440,12 +4440,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>130984</t>
+          <t>132013</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>163388</t>
+          <t>165375</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>18,49%</t>
+          <t>18,63%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>23,34%</t>
         </is>
       </c>
     </row>
@@ -4483,12 +4483,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>110899</t>
+          <t>109085</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>137173</t>
+          <t>136046</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4498,12 +4498,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>39,22%</t>
+          <t>38,58%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>48,51%</t>
+          <t>48,11%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4518,12 +4518,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>180292</t>
+          <t>181237</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>209881</t>
+          <t>211115</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4533,12 +4533,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>42,34%</t>
+          <t>42,56%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>49,29%</t>
+          <t>49,58%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4553,12 +4553,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>299324</t>
+          <t>297316</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>338382</t>
+          <t>336719</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4568,12 +4568,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>42,24%</t>
+          <t>41,96%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>47,75%</t>
+          <t>47,52%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>465601</t>
+          <t>446506</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>657962</t>
+          <t>654071</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>13,46%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>18,91%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>592220</t>
+          <t>598131</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>866976</t>
+          <t>878198</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>16,13%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>23,68%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>1136772</t>
+          <t>1141418</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>1481489</t>
+          <t>1479373</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>20,67%</t>
+          <t>20,64%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>352507</t>
+          <t>345707</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>492777</t>
+          <t>492840</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>14,24%</t>
+          <t>14,25%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>377338</t>
+          <t>375100</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>512781</t>
+          <t>511177</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
@@ -4876,47 +4876,47 @@
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,11%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
+          <t>13,78%</t>
+        </is>
+      </c>
+      <c r="Q40" s="2" t="inlineStr">
+        <is>
+          <t>1223</t>
+        </is>
+      </c>
+      <c r="R40" s="2" t="inlineStr">
+        <is>
+          <t>906202</t>
+        </is>
+      </c>
+      <c r="S40" s="2" t="inlineStr">
+        <is>
+          <t>781012</t>
+        </is>
+      </c>
+      <c r="T40" s="2" t="inlineStr">
+        <is>
+          <t>990492</t>
+        </is>
+      </c>
+      <c r="U40" s="2" t="inlineStr">
+        <is>
+          <t>12,64%</t>
+        </is>
+      </c>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t>10,89%</t>
+        </is>
+      </c>
+      <c r="W40" s="2" t="inlineStr">
+        <is>
           <t>13,82%</t>
-        </is>
-      </c>
-      <c r="Q40" s="2" t="inlineStr">
-        <is>
-          <t>1223</t>
-        </is>
-      </c>
-      <c r="R40" s="2" t="inlineStr">
-        <is>
-          <t>906202</t>
-        </is>
-      </c>
-      <c r="S40" s="2" t="inlineStr">
-        <is>
-          <t>786088</t>
-        </is>
-      </c>
-      <c r="T40" s="2" t="inlineStr">
-        <is>
-          <t>985818</t>
-        </is>
-      </c>
-      <c r="U40" s="2" t="inlineStr">
-        <is>
-          <t>12,64%</t>
-        </is>
-      </c>
-      <c r="V40" s="2" t="inlineStr">
-        <is>
-          <t>10,97%</t>
-        </is>
-      </c>
-      <c r="W40" s="2" t="inlineStr">
-        <is>
-          <t>13,75%</t>
         </is>
       </c>
     </row>
@@ -4939,12 +4939,12 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>489849</t>
+          <t>484051</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>699783</t>
+          <t>698913</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
@@ -4954,12 +4954,12 @@
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>13,99%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>20,23%</t>
+          <t>20,2%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4974,12 +4974,12 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>493712</t>
+          <t>490102</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>675052</t>
+          <t>673658</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
@@ -4989,12 +4989,12 @@
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>18,16%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5009,12 +5009,12 @@
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>1085969</t>
+          <t>1064088</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>1350896</t>
+          <t>1345885</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
@@ -5024,12 +5024,12 @@
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>18,77%</t>
         </is>
       </c>
     </row>
@@ -5052,12 +5052,12 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>1645153</t>
+          <t>1651354</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>2142814</t>
+          <t>2185610</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
@@ -5067,12 +5067,12 @@
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>47,55%</t>
+          <t>47,73%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>61,94%</t>
+          <t>63,18%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5087,12 +5087,12 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>1786584</t>
+          <t>1789669</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>2244576</t>
+          <t>2263394</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
@@ -5102,12 +5102,12 @@
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>48,17%</t>
+          <t>48,25%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>60,51%</t>
+          <t>61,02%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5122,12 +5122,12 @@
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>3501702</t>
+          <t>3475101</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>4196237</t>
+          <t>4185219</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
@@ -5137,12 +5137,12 @@
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>48,85%</t>
+          <t>48,48%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>58,54%</t>
+          <t>58,38%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P04B3_2_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P04B3_2_2023-Edad-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>72036</t>
+          <t>86555</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>51801</t>
+          <t>65611</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>97094</t>
+          <t>113330</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>21,23%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>16,09%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>24,27%</t>
+          <t>27,79%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>59027</t>
+          <t>77334</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>44500</t>
+          <t>59294</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>77455</t>
+          <t>101910</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>18,85%</t>
+          <t>21,33%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>16,36%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>24,73%</t>
+          <t>28,11%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>131063</t>
+          <t>163889</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>104153</t>
+          <t>132599</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>160601</t>
+          <t>194969</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>21,28%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>25,31%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>39349</t>
+          <t>45833</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>23472</t>
+          <t>29000</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>61806</t>
+          <t>70118</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>9,84%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>17,19%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>44071</t>
+          <t>54655</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>29394</t>
+          <t>38681</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>60699</t>
+          <t>75164</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>19,38%</t>
+          <t>20,73%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>83419</t>
+          <t>100488</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>62583</t>
+          <t>76330</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>112314</t>
+          <t>129208</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>15,75%</t>
+          <t>16,77%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>78474</t>
+          <t>71429</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>50854</t>
+          <t>47276</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>111983</t>
+          <t>99304</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>19,62%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>28,0%</t>
+          <t>24,35%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>49426</t>
+          <t>57013</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>33834</t>
+          <t>41075</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>69857</t>
+          <t>79217</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>15,78%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>11,33%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>22,3%</t>
+          <t>21,85%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>127900</t>
+          <t>128442</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>94019</t>
+          <t>96674</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>163455</t>
+          <t>161738</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>16,67%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>13,18%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>22,92%</t>
+          <t>21,0%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>210128</t>
+          <t>203976</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>175909</t>
+          <t>170034</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>243956</t>
+          <t>234853</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>52,53%</t>
+          <t>50,02%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>43,98%</t>
+          <t>41,7%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>60,99%</t>
+          <t>57,59%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>160677</t>
+          <t>173510</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>140016</t>
+          <t>148630</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>184433</t>
+          <t>202166</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>51,3%</t>
+          <t>47,86%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>44,71%</t>
+          <t>41,0%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>58,89%</t>
+          <t>55,77%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>370804</t>
+          <t>377486</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>323744</t>
+          <t>334586</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>410002</t>
+          <t>421514</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>51,99%</t>
+          <t>49,0%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>45,39%</t>
+          <t>43,44%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>57,49%</t>
+          <t>54,72%</t>
         </is>
       </c>
     </row>
@@ -1177,17 +1177,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>399987</t>
+          <t>407793</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1212,17 +1212,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>313200</t>
+          <t>362512</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>713187</t>
+          <t>770305</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>91010</t>
+          <t>107311</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>72391</t>
+          <t>85709</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>113370</t>
+          <t>129819</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>22,58%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>26,78%</t>
+          <t>27,32%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>150746</t>
+          <t>100557</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>89971</t>
+          <t>82766</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>300198</t>
+          <t>119383</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>29,45%</t>
+          <t>20,08%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>16,53%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>58,64%</t>
+          <t>23,84%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>241756</t>
+          <t>207868</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>177075</t>
+          <t>179501</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>386525</t>
+          <t>237372</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>25,85%</t>
+          <t>21,3%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>18,93%</t>
+          <t>18,39%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>41,33%</t>
+          <t>24,32%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>52990</t>
+          <t>60785</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>36308</t>
+          <t>44505</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>70594</t>
+          <t>81077</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>12,52%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>9,36%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>51438</t>
+          <t>57832</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>30147</t>
+          <t>45274</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>68130</t>
+          <t>74826</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>5,89%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>13,31%</t>
+          <t>14,94%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>104428</t>
+          <t>118617</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>77254</t>
+          <t>97149</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>127452</t>
+          <t>144977</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>9,95%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>14,85%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>80358</t>
+          <t>86810</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>60608</t>
+          <t>64478</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>108698</t>
+          <t>109868</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>25,67%</t>
+          <t>23,12%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>85525</t>
+          <t>101474</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>52672</t>
+          <t>83377</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>108305</t>
+          <t>119767</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>16,71%</t>
+          <t>20,26%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>16,65%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>21,16%</t>
+          <t>23,92%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>165883</t>
+          <t>188285</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>129416</t>
+          <t>156638</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>199827</t>
+          <t>220451</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>19,29%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>21,36%</t>
+          <t>22,59%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>199024</t>
+          <t>220342</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>173400</t>
+          <t>191656</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>225714</t>
+          <t>250670</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>47,01%</t>
+          <t>46,36%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>40,96%</t>
+          <t>40,33%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>53,31%</t>
+          <t>52,75%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>224225</t>
+          <t>240894</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>132259</t>
+          <t>216556</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>266348</t>
+          <t>265618</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>43,8%</t>
+          <t>48,11%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>25,84%</t>
+          <t>43,25%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>52,03%</t>
+          <t>53,04%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>423249</t>
+          <t>461236</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>333498</t>
+          <t>426279</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>471031</t>
+          <t>500863</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>45,25%</t>
+          <t>47,26%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>35,66%</t>
+          <t>43,68%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>50,36%</t>
+          <t>51,32%</t>
         </is>
       </c>
     </row>
@@ -1746,17 +1746,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>423382</t>
+          <t>475247</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>423382</t>
+          <t>475247</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>423382</t>
+          <t>475247</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>511934</t>
+          <t>500757</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>511934</t>
+          <t>500757</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>511934</t>
+          <t>500757</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>935316</t>
+          <t>976005</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>935316</t>
+          <t>976005</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>935316</t>
+          <t>976005</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>101160</t>
+          <t>126858</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>83543</t>
+          <t>108439</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>118728</t>
+          <t>150406</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>20,47%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>15,58%</t>
+          <t>17,5%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>22,14%</t>
+          <t>24,27%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>101912</t>
+          <t>117083</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>74691</t>
+          <t>101271</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>119279</t>
+          <t>136355</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>17,24%</t>
+          <t>18,84%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>16,3%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>21,94%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>203071</t>
+          <t>243941</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>171756</t>
+          <t>220255</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>227475</t>
+          <t>274529</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>18,01%</t>
+          <t>19,65%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>17,75%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>22,12%</t>
         </is>
       </c>
     </row>
@@ -1976,32 +1976,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>62990</t>
+          <t>71750</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>49411</t>
+          <t>56527</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>79400</t>
+          <t>90247</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>14,81%</t>
+          <t>14,56%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2011,32 +2011,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>60144</t>
+          <t>70501</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>44050</t>
+          <t>57396</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>75291</t>
+          <t>84447</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>12,74%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2046,32 +2046,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>123134</t>
+          <t>142251</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>102616</t>
+          <t>121164</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>144252</t>
+          <t>163650</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>9,1%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>12,8%</t>
+          <t>13,19%</t>
         </is>
       </c>
     </row>
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>103676</t>
+          <t>116186</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>83271</t>
+          <t>97375</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>121865</t>
+          <t>138045</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>19,34%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,53%</t>
+          <t>15,71%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>22,28%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>98009</t>
+          <t>117864</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>73016</t>
+          <t>101335</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>115449</t>
+          <t>134483</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>18,97%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,35%</t>
+          <t>16,31%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,53%</t>
+          <t>21,64%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>201684</t>
+          <t>234051</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>168365</t>
+          <t>208128</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>229404</t>
+          <t>260038</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>18,86%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>14,94%</t>
+          <t>16,77%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>20,95%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>268348</t>
+          <t>304864</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>245678</t>
+          <t>277415</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>294334</t>
+          <t>329478</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>50,05%</t>
+          <t>49,2%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>45,82%</t>
+          <t>44,77%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>54,9%</t>
+          <t>53,17%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>331047</t>
+          <t>316030</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>299410</t>
+          <t>296245</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>398664</t>
+          <t>338284</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>56,0%</t>
+          <t>50,85%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>50,65%</t>
+          <t>47,67%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>67,44%</t>
+          <t>54,43%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>599395</t>
+          <t>620894</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>560786</t>
+          <t>585176</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>676348</t>
+          <t>652907</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>53,17%</t>
+          <t>50,03%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>49,75%</t>
+          <t>47,15%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>60,0%</t>
+          <t>52,61%</t>
         </is>
       </c>
     </row>
@@ -2315,17 +2315,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>536174</t>
+          <t>619659</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>536174</t>
+          <t>619659</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>536174</t>
+          <t>619659</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2350,17 +2350,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>591111</t>
+          <t>621478</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>591111</t>
+          <t>621478</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>591111</t>
+          <t>621478</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2385,17 +2385,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1127284</t>
+          <t>1241137</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1127284</t>
+          <t>1241137</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1127284</t>
+          <t>1241137</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2432,32 +2432,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>101299</t>
+          <t>117685</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>44932</t>
+          <t>98160</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>149446</t>
+          <t>137619</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>11,41%</t>
+          <t>16,8%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>14,01%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>16,83%</t>
+          <t>19,64%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2467,32 +2467,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>129080</t>
+          <t>141716</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>106532</t>
+          <t>125491</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>150019</t>
+          <t>159040</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>19,29%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14,97%</t>
+          <t>17,08%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>21,64%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,32 +2502,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>230379</t>
+          <t>259401</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>133487</t>
+          <t>234391</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>285670</t>
+          <t>288693</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>14,41%</t>
+          <t>18,07%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>20,11%</t>
         </is>
       </c>
     </row>
@@ -2545,32 +2545,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>94088</t>
+          <t>102364</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>41016</t>
+          <t>83942</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>137930</t>
+          <t>122634</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>14,61%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>17,5%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2580,32 +2580,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>98133</t>
+          <t>110654</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>81477</t>
+          <t>96472</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>112744</t>
+          <t>126868</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>15,06%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,32 +2615,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>192221</t>
+          <t>213018</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>111199</t>
+          <t>189006</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>239567</t>
+          <t>241041</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>16,79%</t>
         </is>
       </c>
     </row>
@@ -2658,32 +2658,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>116770</t>
+          <t>133360</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>48795</t>
+          <t>112075</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>170928</t>
+          <t>156614</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>13,15%</t>
+          <t>19,03%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>22,35%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2693,32 +2693,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>123410</t>
+          <t>135396</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>103958</t>
+          <t>120228</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>141044</t>
+          <t>151576</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>14,61%</t>
+          <t>16,36%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>20,63%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2728,32 +2728,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>240181</t>
+          <t>268756</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>146576</t>
+          <t>242257</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>296126</t>
+          <t>297859</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>15,02%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>9,17%</t>
+          <t>16,88%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>18,52%</t>
+          <t>20,75%</t>
         </is>
       </c>
     </row>
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>575629</t>
+          <t>347208</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>444264</t>
+          <t>317378</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>757394</t>
+          <t>374105</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>64,84%</t>
+          <t>49,56%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>50,04%</t>
+          <t>45,3%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>85,31%</t>
+          <t>53,4%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>360796</t>
+          <t>347031</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>333825</t>
+          <t>325613</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>412001</t>
+          <t>369086</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>50,71%</t>
+          <t>47,23%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>46,92%</t>
+          <t>44,31%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>57,91%</t>
+          <t>50,23%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>936426</t>
+          <t>694240</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>795965</t>
+          <t>658841</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1204651</t>
+          <t>730229</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>58,56%</t>
+          <t>48,37%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>49,77%</t>
+          <t>45,9%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>75,33%</t>
+          <t>50,87%</t>
         </is>
       </c>
     </row>
@@ -2884,17 +2884,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>887786</t>
+          <t>700617</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,17 +2919,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>711419</t>
+          <t>734797</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>711419</t>
+          <t>734797</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>711419</t>
+          <t>734797</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1599206</t>
+          <t>1435415</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1599206</t>
+          <t>1435415</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1599206</t>
+          <t>1435415</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -3001,32 +3001,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>105527</t>
+          <t>117894</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>89659</t>
+          <t>99294</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>123315</t>
+          <t>135319</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>19,35%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>16,3%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>21,97%</t>
+          <t>22,21%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3036,32 +3036,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>110524</t>
+          <t>127691</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>96656</t>
+          <t>111945</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>124563</t>
+          <t>143228</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>20,19%</t>
+          <t>21,0%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>17,66%</t>
+          <t>18,41%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>22,76%</t>
+          <t>23,55%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3071,32 +3071,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>216051</t>
+          <t>245585</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>195630</t>
+          <t>224321</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>239243</t>
+          <t>270563</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>19,49%</t>
+          <t>20,17%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>18,42%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>21,58%</t>
+          <t>22,22%</t>
         </is>
       </c>
     </row>
@@ -3114,32 +3114,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>89096</t>
+          <t>96055</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>74083</t>
+          <t>79577</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>107096</t>
+          <t>111828</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>13,06%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>19,08%</t>
+          <t>18,35%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3149,32 +3149,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>84619</t>
+          <t>94341</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>72317</t>
+          <t>80125</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>98669</t>
+          <t>107355</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>15,51%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>17,65%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3184,32 +3184,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>173716</t>
+          <t>190396</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>154136</t>
+          <t>169991</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>196626</t>
+          <t>213063</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>15,67%</t>
+          <t>15,64%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>17,5%</t>
         </is>
       </c>
     </row>
@@ -3227,32 +3227,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>112945</t>
+          <t>122261</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>96419</t>
+          <t>103647</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>132942</t>
+          <t>142239</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>20,06%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>23,69%</t>
+          <t>23,34%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3262,32 +3262,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>96988</t>
+          <t>108672</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>83867</t>
+          <t>94293</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>110631</t>
+          <t>124544</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>17,72%</t>
+          <t>17,87%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15,32%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>20,21%</t>
+          <t>20,48%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3297,22 +3297,22 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>209934</t>
+          <t>230933</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>188890</t>
+          <t>207451</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>233422</t>
+          <t>256102</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>18,97%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
@@ -3322,7 +3322,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>21,06%</t>
+          <t>21,04%</t>
         </is>
       </c>
     </row>
@@ -3340,32 +3340,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>253665</t>
+          <t>273136</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>230547</t>
+          <t>250050</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>276171</t>
+          <t>295107</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>45,2%</t>
+          <t>44,82%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>41,08%</t>
+          <t>41,04%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>49,21%</t>
+          <t>48,43%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3375,32 +3375,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>255154</t>
+          <t>277444</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>237924</t>
+          <t>260613</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>271476</t>
+          <t>296326</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>46,62%</t>
+          <t>45,62%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>43,47%</t>
+          <t>42,85%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>49,6%</t>
+          <t>48,73%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3410,32 +3410,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>508819</t>
+          <t>550580</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>480068</t>
+          <t>521317</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>537902</t>
+          <t>577822</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>45,9%</t>
+          <t>45,22%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>43,31%</t>
+          <t>42,82%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>48,52%</t>
+          <t>47,46%</t>
         </is>
       </c>
     </row>
@@ -3453,17 +3453,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>561234</t>
+          <t>609346</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>547285</t>
+          <t>608148</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>547285</t>
+          <t>608148</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>547285</t>
+          <t>608148</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>1108519</t>
+          <t>1217494</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1108519</t>
+          <t>1217494</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1108519</t>
+          <t>1217494</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3570,32 +3570,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>70777</t>
+          <t>78051</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>60407</t>
+          <t>65879</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>82748</t>
+          <t>90220</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>19,22%</t>
+          <t>19,17%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>16,41%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>22,48%</t>
+          <t>22,16%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3605,32 +3605,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>68159</t>
+          <t>76999</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>29978</t>
+          <t>64916</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>108226</t>
+          <t>89704</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>17,53%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>20,43%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3640,32 +3640,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>138937</t>
+          <t>155050</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>74825</t>
+          <t>138229</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>183038</t>
+          <t>173737</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>14,23%</t>
+          <t>18,32%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>18,74%</t>
+          <t>20,53%</t>
         </is>
       </c>
     </row>
@@ -3683,32 +3683,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>53940</t>
+          <t>59832</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>43523</t>
+          <t>47794</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>66438</t>
+          <t>73409</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>14,7%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>11,74%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3718,32 +3718,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>59247</t>
+          <t>65533</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>24891</t>
+          <t>55504</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>95216</t>
+          <t>76806</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>14,92%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>17,49%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3753,32 +3753,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>113187</t>
+          <t>125365</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>61289</t>
+          <t>110042</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>150280</t>
+          <t>141863</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>14,81%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>6,28%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>15,39%</t>
+          <t>16,76%</t>
         </is>
       </c>
     </row>
@@ -3796,32 +3796,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>73655</t>
+          <t>82462</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>61607</t>
+          <t>68579</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>87291</t>
+          <t>96661</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>20,26%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>16,73%</t>
+          <t>16,85%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>23,71%</t>
+          <t>23,74%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3831,32 +3831,32 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>73185</t>
+          <t>79807</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>33478</t>
+          <t>68873</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>116996</t>
+          <t>92282</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>18,17%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3866,32 +3866,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>146841</t>
+          <t>162269</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>78197</t>
+          <t>143469</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>193348</t>
+          <t>181034</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>15,04%</t>
+          <t>19,18%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>19,8%</t>
+          <t>21,39%</t>
         </is>
       </c>
     </row>
@@ -3909,32 +3909,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>169792</t>
+          <t>186735</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>154947</t>
+          <t>169324</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>184994</t>
+          <t>203857</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>46,12%</t>
+          <t>45,87%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>42,09%</t>
+          <t>41,59%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>50,25%</t>
+          <t>50,08%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3944,32 +3944,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>407776</t>
+          <t>216827</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>297350</t>
+          <t>202799</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>515999</t>
+          <t>232222</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>67,03%</t>
+          <t>49,37%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>48,88%</t>
+          <t>46,18%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>84,82%</t>
+          <t>52,88%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3979,32 +3979,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>577569</t>
+          <t>403561</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>462827</t>
+          <t>380618</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>760170</t>
+          <t>427389</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>59,14%</t>
+          <t>47,69%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>47,39%</t>
+          <t>44,98%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>77,84%</t>
+          <t>50,5%</t>
         </is>
       </c>
     </row>
@@ -4022,17 +4022,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>368165</t>
+          <t>407080</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4057,17 +4057,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>608368</t>
+          <t>439166</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4092,17 +4092,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>976533</t>
+          <t>846246</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4139,32 +4139,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>50197</t>
+          <t>55364</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>40779</t>
+          <t>45024</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>60467</t>
+          <t>66528</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>17,85%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>21,38%</t>
+          <t>21,45%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4174,32 +4174,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>76120</t>
+          <t>85604</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>65626</t>
+          <t>72600</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>89212</t>
+          <t>97980</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>15,63%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>20,95%</t>
+          <t>21,09%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4209,32 +4209,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>126317</t>
+          <t>140969</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>113230</t>
+          <t>125097</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>142238</t>
+          <t>160365</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>17,83%</t>
+          <t>18,19%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>15,98%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>20,7%</t>
         </is>
       </c>
     </row>
@@ -4252,32 +4252,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>47634</t>
+          <t>52633</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>37602</t>
+          <t>42037</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>58362</t>
+          <t>65328</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>16,85%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>13,3%</t>
+          <t>13,55%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>21,06%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4287,32 +4287,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>68463</t>
+          <t>76349</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>58666</t>
+          <t>65310</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>78602</t>
+          <t>89219</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>14,06%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>18,46%</t>
+          <t>19,2%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4322,32 +4322,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>116097</t>
+          <t>128983</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>101178</t>
+          <t>113636</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>130536</t>
+          <t>146290</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>16,65%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>18,88%</t>
         </is>
       </c>
     </row>
@@ -4365,32 +4365,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>62284</t>
+          <t>70152</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>50552</t>
+          <t>58082</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>74054</t>
+          <t>82545</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>22,62%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>26,19%</t>
+          <t>26,61%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4400,32 +4400,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>85878</t>
+          <t>95187</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>75320</t>
+          <t>82450</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>98475</t>
+          <t>109621</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>20,17%</t>
+          <t>20,49%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>17,69%</t>
+          <t>17,75%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>23,13%</t>
+          <t>23,59%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4435,32 +4435,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>148161</t>
+          <t>165339</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>132013</t>
+          <t>147975</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>165375</t>
+          <t>185425</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>21,34%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>19,1%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>23,34%</t>
+          <t>23,93%</t>
         </is>
       </c>
     </row>
@@ -4478,32 +4478,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>122644</t>
+          <t>132049</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>109085</t>
+          <t>117259</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>136046</t>
+          <t>147117</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>43,37%</t>
+          <t>42,57%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>38,58%</t>
+          <t>37,8%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>48,11%</t>
+          <t>47,43%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4513,32 +4513,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>195370</t>
+          <t>207469</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>181237</t>
+          <t>192240</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>211115</t>
+          <t>223841</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>45,88%</t>
+          <t>44,65%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>42,56%</t>
+          <t>41,38%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>49,58%</t>
+          <t>48,18%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4548,32 +4548,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>318014</t>
+          <t>339517</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>297316</t>
+          <t>318090</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>336719</t>
+          <t>362112</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>44,88%</t>
+          <t>43,82%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>41,96%</t>
+          <t>41,05%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>47,52%</t>
+          <t>46,74%</t>
         </is>
       </c>
     </row>
@@ -4591,17 +4591,17 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>282759</t>
+          <t>310198</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4626,17 +4626,17 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>425831</t>
+          <t>464609</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4661,17 +4661,17 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>708590</t>
+          <t>774807</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
@@ -4708,32 +4708,32 @@
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>592007</t>
+          <t>689718</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>446506</t>
+          <t>641930</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>654071</t>
+          <t>741806</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>19,54%</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>18,19%</t>
         </is>
       </c>
       <c r="I39" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="J39" s="2" t="inlineStr">
@@ -4743,32 +4743,32 @@
       </c>
       <c r="K39" s="2" t="inlineStr">
         <is>
-          <t>695567</t>
+          <t>726985</t>
         </is>
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>598131</t>
+          <t>688236</t>
         </is>
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>878198</t>
+          <t>773570</t>
         </is>
       </c>
       <c r="N39" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>19,48%</t>
         </is>
       </c>
       <c r="O39" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="P39" s="2" t="inlineStr">
         <is>
-          <t>23,68%</t>
+          <t>20,73%</t>
         </is>
       </c>
       <c r="Q39" s="2" t="inlineStr">
@@ -4778,32 +4778,32 @@
       </c>
       <c r="R39" s="2" t="inlineStr">
         <is>
-          <t>1287574</t>
+          <t>1416703</t>
         </is>
       </c>
       <c r="S39" s="2" t="inlineStr">
         <is>
-          <t>1141418</t>
+          <t>1354131</t>
         </is>
       </c>
       <c r="T39" s="2" t="inlineStr">
         <is>
-          <t>1479373</t>
+          <t>1485203</t>
         </is>
       </c>
       <c r="U39" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>19,51%</t>
         </is>
       </c>
       <c r="V39" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>18,65%</t>
         </is>
       </c>
       <c r="W39" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>20,45%</t>
         </is>
       </c>
     </row>
@@ -4821,32 +4821,32 @@
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>440088</t>
+          <t>489252</t>
         </is>
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>345707</t>
+          <t>444064</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>492840</t>
+          <t>530529</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
         <is>
-          <t>12,72%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>9,99%</t>
+          <t>12,58%</t>
         </is>
       </c>
       <c r="I40" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>15,03%</t>
         </is>
       </c>
       <c r="J40" s="2" t="inlineStr">
@@ -4856,32 +4856,32 @@
       </c>
       <c r="K40" s="2" t="inlineStr">
         <is>
-          <t>466114</t>
+          <t>529865</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>375100</t>
+          <t>492351</t>
         </is>
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>511177</t>
+          <t>567830</t>
         </is>
       </c>
       <c r="N40" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>14,2%</t>
         </is>
       </c>
       <c r="O40" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="P40" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>15,22%</t>
         </is>
       </c>
       <c r="Q40" s="2" t="inlineStr">
@@ -4891,32 +4891,32 @@
       </c>
       <c r="R40" s="2" t="inlineStr">
         <is>
-          <t>906202</t>
+          <t>1019117</t>
         </is>
       </c>
       <c r="S40" s="2" t="inlineStr">
         <is>
-          <t>781012</t>
+          <t>962535</t>
         </is>
       </c>
       <c r="T40" s="2" t="inlineStr">
         <is>
-          <t>990492</t>
+          <t>1077239</t>
         </is>
       </c>
       <c r="U40" s="2" t="inlineStr">
         <is>
-          <t>12,64%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="V40" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>13,26%</t>
         </is>
       </c>
       <c r="W40" s="2" t="inlineStr">
         <is>
-          <t>13,82%</t>
+          <t>14,84%</t>
         </is>
       </c>
     </row>
@@ -4934,32 +4934,32 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>628162</t>
+          <t>682661</t>
         </is>
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>484051</t>
+          <t>629727</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
-          <t>698913</t>
+          <t>737750</t>
         </is>
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>19,34%</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>13,99%</t>
+          <t>17,84%</t>
         </is>
       </c>
       <c r="I41" s="2" t="inlineStr">
         <is>
-          <t>20,2%</t>
+          <t>20,9%</t>
         </is>
       </c>
       <c r="J41" s="2" t="inlineStr">
@@ -4969,32 +4969,32 @@
       </c>
       <c r="K41" s="2" t="inlineStr">
         <is>
-          <t>612421</t>
+          <t>695413</t>
         </is>
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>490102</t>
+          <t>653627</t>
         </is>
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>673658</t>
+          <t>736934</t>
         </is>
       </c>
       <c r="N41" s="2" t="inlineStr">
         <is>
-          <t>16,51%</t>
+          <t>18,64%</t>
         </is>
       </c>
       <c r="O41" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>17,52%</t>
         </is>
       </c>
       <c r="P41" s="2" t="inlineStr">
         <is>
-          <t>18,16%</t>
+          <t>19,75%</t>
         </is>
       </c>
       <c r="Q41" s="2" t="inlineStr">
@@ -5004,32 +5004,32 @@
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>1240583</t>
+          <t>1378074</t>
         </is>
       </c>
       <c r="S41" s="2" t="inlineStr">
         <is>
-          <t>1064088</t>
+          <t>1314409</t>
         </is>
       </c>
       <c r="T41" s="2" t="inlineStr">
         <is>
-          <t>1345885</t>
+          <t>1448793</t>
         </is>
       </c>
       <c r="U41" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>18,98%</t>
         </is>
       </c>
       <c r="V41" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>18,1%</t>
         </is>
       </c>
       <c r="W41" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>19,95%</t>
         </is>
       </c>
     </row>
@@ -5047,32 +5047,32 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>1799231</t>
+          <t>1668310</t>
         </is>
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>1651354</t>
+          <t>1604490</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
-          <t>2185610</t>
+          <t>1740686</t>
         </is>
       </c>
       <c r="G42" s="2" t="inlineStr">
         <is>
-          <t>52,01%</t>
+          <t>47,26%</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>47,73%</t>
+          <t>45,45%</t>
         </is>
       </c>
       <c r="I42" s="2" t="inlineStr">
         <is>
-          <t>63,18%</t>
+          <t>49,31%</t>
         </is>
       </c>
       <c r="J42" s="2" t="inlineStr">
@@ -5082,32 +5082,32 @@
       </c>
       <c r="K42" s="2" t="inlineStr">
         <is>
-          <t>1935045</t>
+          <t>1779205</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>1789669</t>
+          <t>1721265</t>
         </is>
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>2263394</t>
+          <t>1830214</t>
         </is>
       </c>
       <c r="N42" s="2" t="inlineStr">
         <is>
-          <t>52,17%</t>
+          <t>47,68%</t>
         </is>
       </c>
       <c r="O42" s="2" t="inlineStr">
         <is>
-          <t>48,25%</t>
+          <t>46,13%</t>
         </is>
       </c>
       <c r="P42" s="2" t="inlineStr">
         <is>
-          <t>61,02%</t>
+          <t>49,05%</t>
         </is>
       </c>
       <c r="Q42" s="2" t="inlineStr">
@@ -5117,32 +5117,32 @@
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>3734276</t>
+          <t>3447514</t>
         </is>
       </c>
       <c r="S42" s="2" t="inlineStr">
         <is>
-          <t>3475101</t>
+          <t>3371320</t>
         </is>
       </c>
       <c r="T42" s="2" t="inlineStr">
         <is>
-          <t>4185219</t>
+          <t>3530460</t>
         </is>
       </c>
       <c r="U42" s="2" t="inlineStr">
         <is>
-          <t>52,09%</t>
+          <t>47,48%</t>
         </is>
       </c>
       <c r="V42" s="2" t="inlineStr">
         <is>
-          <t>48,48%</t>
+          <t>46,43%</t>
         </is>
       </c>
       <c r="W42" s="2" t="inlineStr">
         <is>
-          <t>58,38%</t>
+          <t>48,62%</t>
         </is>
       </c>
     </row>
@@ -5160,17 +5160,17 @@
       </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>3459488</t>
+          <t>3529941</t>
         </is>
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>3459488</t>
+          <t>3529941</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
         <is>
-          <t>3459488</t>
+          <t>3529941</t>
         </is>
       </c>
       <c r="G43" s="2" t="inlineStr">
@@ -5195,17 +5195,17 @@
       </c>
       <c r="K43" s="2" t="inlineStr">
         <is>
-          <t>3709148</t>
+          <t>3731467</t>
         </is>
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>3709148</t>
+          <t>3731467</t>
         </is>
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>3709148</t>
+          <t>3731467</t>
         </is>
       </c>
       <c r="N43" s="2" t="inlineStr">
@@ -5230,17 +5230,17 @@
       </c>
       <c r="R43" s="2" t="inlineStr">
         <is>
-          <t>7168635</t>
+          <t>7261408</t>
         </is>
       </c>
       <c r="S43" s="2" t="inlineStr">
         <is>
-          <t>7168635</t>
+          <t>7261408</t>
         </is>
       </c>
       <c r="T43" s="2" t="inlineStr">
         <is>
-          <t>7168635</t>
+          <t>7261408</t>
         </is>
       </c>
       <c r="U43" s="2" t="inlineStr">
